--- a/assets/constructions/examples/ctd_tsmb_bush.xlsx
+++ b/assets/constructions/examples/ctd_tsmb_bush.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,11 +579,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MHCR22-6-4F</t>
+          <t>MHC12-6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -597,7 +617,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
         <v>6</v>
@@ -609,18 +629,20 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>20</v>
+        <v>10.8</v>
       </c>
       <c r="M2" t="n">
-        <v>20</v>
+        <v>10.8</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>22</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="P2" t="n">
+        <v>16</v>
+      </c>
       <c r="Q2" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -632,7 +654,7 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>ISO_5609:22</t>
+          <t>ISO_5609:12</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -663,11 +685,25 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>10774.63</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MHC10-4</t>
+          <t>MHC0875-4-4F</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -681,7 +717,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>22.25</v>
       </c>
       <c r="E3" t="n">
         <v>4</v>
@@ -693,20 +729,18 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>8.800000000000001</v>
+        <v>20.828</v>
       </c>
       <c r="M3" t="n">
-        <v>8.800000000000001</v>
+        <v>23.495</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>10</v>
-      </c>
-      <c r="P3" t="n">
-        <v>14</v>
-      </c>
+        <v>23.495</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>65</v>
+        <v>83.566</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -718,7 +752,7 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>ISO_5609:10</t>
+          <t>ISO_5609:23.495</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -736,9 +770,7 @@
           <t>VARGUS</t>
         </is>
       </c>
-      <c r="Z3" t="b">
-        <v>0</v>
-      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
@@ -746,14 +778,28 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2019 / Groovex Catalog</t>
-        </is>
+          <t>2022/ GROOVEX Microscope</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>10774.63</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MHC1000-4-4F</t>
+          <t>MHC0625-8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -767,10 +813,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25.4</v>
+        <v>15.875</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -779,18 +825,20 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>22.86</v>
+        <v>14.808</v>
       </c>
       <c r="M4" t="n">
-        <v>27</v>
+        <v>15.875</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>27</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
+        <v>15.875</v>
+      </c>
+      <c r="P4" t="n">
+        <v>18.593</v>
+      </c>
       <c r="Q4" t="n">
-        <v>109.98</v>
+        <v>42.34</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -802,17 +850,17 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>ISO_5609:27</t>
+          <t>ISO_5609:15.875</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>VARGUS_D:4</t>
+          <t>VARGUS_D:8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>VAR_MICR:4</t>
+          <t>VAR_MICR:8</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -828,14 +876,28 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2022/ GROOVEX Microscope</t>
-        </is>
+          <t>2022 / GROOVEX Mini-V</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>10774.63</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MHC0625-4</t>
+          <t>MHCS22-6-4F</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -849,10 +911,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.205</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -861,20 +923,20 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>13.995</v>
+        <v>20</v>
       </c>
       <c r="M5" t="n">
-        <v>16.205</v>
+        <v>20</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>16.205</v>
+        <v>24.7</v>
       </c>
       <c r="P5" t="n">
-        <v>18.593</v>
+        <v>22</v>
       </c>
       <c r="Q5" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -886,17 +948,17 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>ISO_5609:16.2052</t>
+          <t>ISO_5609:22</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>VARGUS_D:4</t>
+          <t>VARGUS_D:6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>VAR_MICR:4</t>
+          <t>VAR_MICR:6</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -904,7 +966,9 @@
           <t>VARGUS</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr"/>
+      <c r="Z5" t="b">
+        <v>0</v>
+      </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
@@ -912,14 +976,28 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2022 / GROOVEX Mini-V</t>
-        </is>
+          <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>146.48</v>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>13466.45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MHC0750-5</t>
+          <t>MHC25-7-4F</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -933,10 +1011,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21.006</v>
+        <v>25</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -945,20 +1023,18 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>18.009</v>
+        <v>23</v>
       </c>
       <c r="M6" t="n">
-        <v>21.006</v>
+        <v>23</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>21.006</v>
-      </c>
-      <c r="P6" t="n">
-        <v>21.006</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>89.98999999999999</v>
+        <v>110</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -970,17 +1046,17 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>ISO_5609:21</t>
+          <t>ISO_5609:25</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>VARGUS_D:5</t>
+          <t>VARGUS_D:7</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>VAR_MICR:5</t>
+          <t>VAR_MICR:7</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -988,7 +1064,9 @@
           <t>VARGUS</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr"/>
+      <c r="Z6" t="b">
+        <v>0</v>
+      </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
@@ -996,8 +1074,22 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2022 / GROOVEX Mini-V</t>
-        </is>
+          <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>10774.63</v>
       </c>
     </row>
   </sheetData>
